--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655249</v>
+        <v>124652643</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,43 +915,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597121</v>
+        <v>597090</v>
       </c>
       <c r="R4" t="n">
-        <v>6924061</v>
+        <v>6924039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652643</v>
+        <v>124655249</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,46 +1025,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597090</v>
+        <v>597121</v>
       </c>
       <c r="R5" t="n">
-        <v>6924039</v>
+        <v>6924061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124654038</v>
+        <v>124652643</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,43 +808,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597211</v>
+        <v>597090</v>
       </c>
       <c r="R3" t="n">
-        <v>6924014</v>
+        <v>6924039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124652643</v>
+        <v>124654038</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +918,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597090</v>
+        <v>597211</v>
       </c>
       <c r="R4" t="n">
-        <v>6924039</v>
+        <v>6924014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124652643</v>
+        <v>124654038</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,46 +808,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597090</v>
+        <v>597211</v>
       </c>
       <c r="R3" t="n">
-        <v>6924039</v>
+        <v>6924014</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124654038</v>
+        <v>124655249</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -951,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597211</v>
+        <v>597121</v>
       </c>
       <c r="R4" t="n">
-        <v>6924014</v>
+        <v>6924061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124655249</v>
+        <v>124652643</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,43 +1022,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597121</v>
+        <v>597090</v>
       </c>
       <c r="R5" t="n">
-        <v>6924061</v>
+        <v>6924039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124654038</v>
+        <v>124655249</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597211</v>
+        <v>597121</v>
       </c>
       <c r="R3" t="n">
-        <v>6924014</v>
+        <v>6924061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655249</v>
+        <v>124652643</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,43 +915,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597121</v>
+        <v>597090</v>
       </c>
       <c r="R4" t="n">
-        <v>6924061</v>
+        <v>6924039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652643</v>
+        <v>124653753</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,46 +1025,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597090</v>
+        <v>597211</v>
       </c>
       <c r="R5" t="n">
-        <v>6924039</v>
+        <v>6924014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,6 +1118,2071 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124943857</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>597272</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6923991</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124941680</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>597208</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6923937</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124943230</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>597393</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6923922</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124941987</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>597306</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6923901</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124942008</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>597242</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6923954</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124942395</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96982</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>597242</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6923954</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124941910</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90962</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>112</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>597113</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6924130</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124944217</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98124</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>597242</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6923954</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124943491</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91023</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Spillkråka, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>597211</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6924014</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124941477</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>597188</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6923937</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124944576</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>597079</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6924029</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124941214</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>597182</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6923894</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124942320</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>597221</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6924056</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124941126</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>597146</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6923918</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124941301</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>597175</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6923914</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124941736</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>597185</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6923934</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124943798</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79795</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597302</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6923956</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124942488</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>597356</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6923925</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124943230</v>
+        <v>124941987</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,43 +1361,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597393</v>
+        <v>597306</v>
       </c>
       <c r="R8" t="n">
-        <v>6923922</v>
+        <v>6923901</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,22 +1449,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124941987</v>
+        <v>124943230</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,38 +1473,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597306</v>
+        <v>597393</v>
       </c>
       <c r="R9" t="n">
-        <v>6923901</v>
+        <v>6923922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2142,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124941477</v>
+        <v>124944576</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,34 +2158,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597188</v>
+        <v>597079</v>
       </c>
       <c r="R15" t="n">
-        <v>6923937</v>
+        <v>6924029</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2217,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2227,7 +2232,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,22 +2252,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124944576</v>
+        <v>124941477</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,39 +2280,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597079</v>
+        <v>597188</v>
       </c>
       <c r="R16" t="n">
-        <v>6924029</v>
+        <v>6923937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2344,12 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,12 +2364,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124655249</v>
+        <v>124654038</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597121</v>
+        <v>597211</v>
       </c>
       <c r="R3" t="n">
-        <v>6924061</v>
+        <v>6924014</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124652643</v>
+        <v>124655249</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +915,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597090</v>
+        <v>597121</v>
       </c>
       <c r="R4" t="n">
-        <v>6924039</v>
+        <v>6924061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124653753</v>
+        <v>124652643</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,43 +1022,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597211</v>
+        <v>597090</v>
       </c>
       <c r="R5" t="n">
-        <v>6924014</v>
+        <v>6924039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124943857</v>
+        <v>124941987</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,39 +1136,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597272</v>
+        <v>597306</v>
       </c>
       <c r="R6" t="n">
-        <v>6923991</v>
+        <v>6923901</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124941680</v>
+        <v>124942395</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>96982</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,38 +1244,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597208</v>
+        <v>597242</v>
       </c>
       <c r="R7" t="n">
-        <v>6923937</v>
+        <v>6923954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,19 +1336,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124941987</v>
+        <v>124942320</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1389,13 +1388,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597306</v>
+        <v>597221</v>
       </c>
       <c r="R8" t="n">
-        <v>6923901</v>
+        <v>6924056</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,12 +1448,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1578,7 +1577,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124942008</v>
+        <v>124943440</v>
       </c>
       <c r="B10" t="n">
         <v>79891</v>
@@ -1653,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124942395</v>
+        <v>124941126</v>
       </c>
       <c r="B11" t="n">
-        <v>96982</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,42 +1701,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597242</v>
+        <v>597146</v>
       </c>
       <c r="R11" t="n">
-        <v>6923954</v>
+        <v>6923918</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,7 +1779,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,22 +1799,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124941910</v>
+        <v>124944576</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,37 +1827,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597113</v>
+        <v>597079</v>
       </c>
       <c r="R12" t="n">
-        <v>6924130</v>
+        <v>6924029</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1881,7 +1891,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,7 +1901,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,22 +1921,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124944217</v>
+        <v>124941477</v>
       </c>
       <c r="B13" t="n">
-        <v>98124</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,38 +1945,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597242</v>
+        <v>597188</v>
       </c>
       <c r="R13" t="n">
-        <v>6923954</v>
+        <v>6923937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,22 +2033,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124943491</v>
+        <v>124941301</v>
       </c>
       <c r="B14" t="n">
-        <v>91023</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,34 +2061,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597211</v>
+        <v>597175</v>
       </c>
       <c r="R14" t="n">
-        <v>6924014</v>
+        <v>6923914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2135,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124944576</v>
+        <v>124941736</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,39 +2178,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597079</v>
+        <v>597185</v>
       </c>
       <c r="R15" t="n">
-        <v>6924029</v>
+        <v>6923934</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,12 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,19 +2262,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124941477</v>
+        <v>124941214</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2304,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597188</v>
+        <v>597182</v>
       </c>
       <c r="R16" t="n">
-        <v>6923937</v>
+        <v>6923894</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124941214</v>
+        <v>124942488</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,34 +2402,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597182</v>
+        <v>597356</v>
       </c>
       <c r="R17" t="n">
-        <v>6923894</v>
+        <v>6923925</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2466,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2476,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,22 +2496,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124942320</v>
+        <v>124943857</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2504,37 +2524,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597221</v>
+        <v>597272</v>
       </c>
       <c r="R18" t="n">
-        <v>6924056</v>
+        <v>6923991</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2598,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,22 +2613,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124941126</v>
+        <v>124943798</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,46 +2637,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597146</v>
+        <v>597302</v>
       </c>
       <c r="R19" t="n">
-        <v>6923918</v>
+        <v>6923956</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2680,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2690,12 +2710,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,22 +2725,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124941301</v>
+        <v>124941910</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>90962</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,46 +2749,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>112</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597175</v>
+        <v>597113</v>
       </c>
       <c r="R20" t="n">
-        <v>6923914</v>
+        <v>6924130</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2802,7 +2812,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2822,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,22 +2837,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124941736</v>
+        <v>124941680</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,34 +2865,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597185</v>
+        <v>597208</v>
       </c>
       <c r="R21" t="n">
-        <v>6923934</v>
+        <v>6923937</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2924,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2934,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,22 +2949,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124943798</v>
+        <v>124943491</v>
       </c>
       <c r="B22" t="n">
-        <v>79795</v>
+        <v>91023</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2967,37 +2977,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597302</v>
+        <v>597211</v>
       </c>
       <c r="R22" t="n">
-        <v>6923956</v>
+        <v>6924014</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3026,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3046,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,22 +3061,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124942488</v>
+        <v>124944217</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>98124</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3075,43 +3085,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597356</v>
+        <v>597242</v>
       </c>
       <c r="R23" t="n">
-        <v>6923925</v>
+        <v>6923954</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3143,7 +3148,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3153,12 +3158,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124654038</v>
+        <v>124655249</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597211</v>
+        <v>597121</v>
       </c>
       <c r="R3" t="n">
-        <v>6924014</v>
+        <v>6924061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655249</v>
+        <v>124654038</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597121</v>
+        <v>597211</v>
       </c>
       <c r="R4" t="n">
-        <v>6924061</v>
+        <v>6924014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124941987</v>
+        <v>124944217</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98124</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,38 +1132,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597306</v>
+        <v>597242</v>
       </c>
       <c r="R6" t="n">
-        <v>6923901</v>
+        <v>6923954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,22 +1220,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124942395</v>
+        <v>124942008</v>
       </c>
       <c r="B7" t="n">
-        <v>96982</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,32 +1244,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -1311,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124942320</v>
+        <v>124941736</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1384,17 +1380,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597221</v>
+        <v>597185</v>
       </c>
       <c r="R8" t="n">
-        <v>6924056</v>
+        <v>6923934</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1433,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,22 +1444,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124943230</v>
+        <v>124943491</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,39 +1472,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597393</v>
+        <v>597211</v>
       </c>
       <c r="R9" t="n">
-        <v>6923922</v>
+        <v>6924014</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,7 +1541,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124943440</v>
+        <v>124942320</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,37 +1584,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597242</v>
+        <v>597221</v>
       </c>
       <c r="R10" t="n">
-        <v>6923954</v>
+        <v>6924056</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,7 +1643,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1653,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,22 +1668,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124941126</v>
+        <v>124941910</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,42 +1696,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597146</v>
+        <v>597113</v>
       </c>
       <c r="R11" t="n">
-        <v>6923918</v>
+        <v>6924130</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1769,7 +1755,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,12 +1765,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,22 +1780,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124944576</v>
+        <v>124941680</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,39 +1808,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597079</v>
+        <v>597208</v>
       </c>
       <c r="R12" t="n">
-        <v>6924029</v>
+        <v>6923937</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,12 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941477</v>
+        <v>124944576</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,34 +1920,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597188</v>
+        <v>597079</v>
       </c>
       <c r="R13" t="n">
-        <v>6923937</v>
+        <v>6924029</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +1984,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +1994,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,22 +2014,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124941301</v>
+        <v>124943230</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,27 +2042,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2090,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597175</v>
+        <v>597393</v>
       </c>
       <c r="R14" t="n">
-        <v>6923914</v>
+        <v>6923922</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2106,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2116,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124941736</v>
+        <v>124941301</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,38 +2155,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597185</v>
+        <v>597175</v>
       </c>
       <c r="R15" t="n">
-        <v>6923934</v>
+        <v>6923914</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,7 +2223,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2233,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,7 +2260,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124941214</v>
+        <v>124941477</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2314,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597182</v>
+        <v>597188</v>
       </c>
       <c r="R16" t="n">
-        <v>6923894</v>
+        <v>6923937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2345,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2372,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124942488</v>
+        <v>124941214</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,39 +2388,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597356</v>
+        <v>597182</v>
       </c>
       <c r="R17" t="n">
-        <v>6923925</v>
+        <v>6923894</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2476,12 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,22 +2472,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124943857</v>
+        <v>124941126</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,16 +2500,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2553,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597272</v>
+        <v>597146</v>
       </c>
       <c r="R18" t="n">
-        <v>6923991</v>
+        <v>6923918</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,7 +2574,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,12 +2594,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2737,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124941910</v>
+        <v>124942488</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2753,37 +2734,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597113</v>
+        <v>597356</v>
       </c>
       <c r="R20" t="n">
-        <v>6924130</v>
+        <v>6923925</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2812,7 +2798,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2822,7 +2808,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,22 +2828,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124941680</v>
+        <v>124941987</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,21 +2856,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2889,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597208</v>
+        <v>597306</v>
       </c>
       <c r="R21" t="n">
-        <v>6923937</v>
+        <v>6923901</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,7 +2915,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2934,7 +2925,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,22 +2940,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124943491</v>
+        <v>124943857</v>
       </c>
       <c r="B22" t="n">
-        <v>91023</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2973,38 +2964,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597211</v>
+        <v>597272</v>
       </c>
       <c r="R22" t="n">
-        <v>6924014</v>
+        <v>6923991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,7 +3032,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3046,7 +3042,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,22 +3057,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124944217</v>
+        <v>124942395</v>
       </c>
       <c r="B23" t="n">
-        <v>98124</v>
+        <v>96982</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3089,24 +3085,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>221946</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124942320</v>
+        <v>124941910</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597221</v>
+        <v>597113</v>
       </c>
       <c r="R10" t="n">
-        <v>6924056</v>
+        <v>6924130</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124941910</v>
+        <v>124942320</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597113</v>
+        <v>597221</v>
       </c>
       <c r="R11" t="n">
-        <v>6924130</v>
+        <v>6924056</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124943230</v>
+        <v>124941301</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,27 +2042,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597393</v>
+        <v>597175</v>
       </c>
       <c r="R14" t="n">
-        <v>6923922</v>
+        <v>6923914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,10 +2143,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124941301</v>
+        <v>124943230</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>57883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,27 +2159,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597175</v>
+        <v>597393</v>
       </c>
       <c r="R15" t="n">
-        <v>6923914</v>
+        <v>6923922</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2606,10 +2606,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124943798</v>
+        <v>124942488</v>
       </c>
       <c r="B19" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2618,41 +2618,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597302</v>
+        <v>597356</v>
       </c>
       <c r="R19" t="n">
-        <v>6923956</v>
+        <v>6923925</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2681,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2691,7 +2696,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,22 +2716,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124942488</v>
+        <v>124943798</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2730,46 +2740,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597356</v>
+        <v>597302</v>
       </c>
       <c r="R20" t="n">
-        <v>6923925</v>
+        <v>6923956</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2798,7 +2803,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2808,12 +2813,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,12 +2828,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124655249</v>
+        <v>124652643</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,43 +808,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597121</v>
+        <v>597090</v>
       </c>
       <c r="R3" t="n">
-        <v>6924061</v>
+        <v>6924039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1010,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652643</v>
+        <v>124655249</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,46 +1025,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597090</v>
+        <v>597121</v>
       </c>
       <c r="R5" t="n">
-        <v>6924039</v>
+        <v>6924061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124944217</v>
+        <v>124943440</v>
       </c>
       <c r="B6" t="n">
-        <v>98124</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1132,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124942008</v>
+        <v>124941680</v>
       </c>
       <c r="B7" t="n">
         <v>79891</v>
@@ -1268,14 +1268,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597242</v>
+        <v>597208</v>
       </c>
       <c r="R7" t="n">
-        <v>6923954</v>
+        <v>6923937</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,22 +1332,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124941736</v>
+        <v>124943230</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,38 +1356,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597185</v>
+        <v>597393</v>
       </c>
       <c r="R8" t="n">
-        <v>6923934</v>
+        <v>6923922</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124943491</v>
+        <v>124944576</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,38 +1473,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597211</v>
+        <v>597079</v>
       </c>
       <c r="R9" t="n">
-        <v>6924014</v>
+        <v>6924029</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1541,7 +1551,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,12 +1571,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1680,7 +1695,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124942320</v>
+        <v>124941987</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1720,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597221</v>
+        <v>597306</v>
       </c>
       <c r="R11" t="n">
-        <v>6924056</v>
+        <v>6923901</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1765,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,22 +1795,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124941680</v>
+        <v>124941126</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,34 +1823,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597208</v>
+        <v>597146</v>
       </c>
       <c r="R12" t="n">
-        <v>6923937</v>
+        <v>6923918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1877,7 +1897,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124944576</v>
+        <v>124941214</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1920,39 +1945,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597079</v>
+        <v>597182</v>
       </c>
       <c r="R13" t="n">
-        <v>6924029</v>
+        <v>6923894</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1994,12 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,22 +2029,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124941301</v>
+        <v>124944217</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>98124</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,39 +2057,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597175</v>
+        <v>597242</v>
       </c>
       <c r="R14" t="n">
-        <v>6923914</v>
+        <v>6923954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2116,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,22 +2141,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124943230</v>
+        <v>124941477</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,43 +2165,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597393</v>
+        <v>597188</v>
       </c>
       <c r="R15" t="n">
-        <v>6923922</v>
+        <v>6923937</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2233,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,22 +2253,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124941477</v>
+        <v>124943798</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,25 +2277,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2300,13 +2305,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597188</v>
+        <v>597302</v>
       </c>
       <c r="R16" t="n">
-        <v>6923937</v>
+        <v>6923956</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2335,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,22 +2365,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124941214</v>
+        <v>124943857</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,34 +2393,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597182</v>
+        <v>597272</v>
       </c>
       <c r="R17" t="n">
-        <v>6923894</v>
+        <v>6923991</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,7 +2457,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2467,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,10 +2494,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124941126</v>
+        <v>124941301</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,43 +2506,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597146</v>
+        <v>597175</v>
       </c>
       <c r="R18" t="n">
-        <v>6923918</v>
+        <v>6923914</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,12 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,22 +2599,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124942488</v>
+        <v>124942320</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,42 +2627,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597356</v>
+        <v>597221</v>
       </c>
       <c r="R19" t="n">
-        <v>6923925</v>
+        <v>6924056</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,12 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,22 +2711,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124943798</v>
+        <v>124942395</v>
       </c>
       <c r="B20" t="n">
-        <v>79795</v>
+        <v>96982</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,37 +2739,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>221946</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597302</v>
+        <v>597242</v>
       </c>
       <c r="R20" t="n">
-        <v>6923956</v>
+        <v>6923954</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2803,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2813,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2828,22 +2827,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124941987</v>
+        <v>124942488</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2856,34 +2855,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597306</v>
+        <v>597356</v>
       </c>
       <c r="R21" t="n">
-        <v>6923901</v>
+        <v>6923925</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,7 +2919,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2925,7 +2929,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2940,22 +2949,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124943857</v>
+        <v>124941736</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2968,39 +2977,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597272</v>
+        <v>597185</v>
       </c>
       <c r="R22" t="n">
-        <v>6923991</v>
+        <v>6923934</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3032,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,7 +3046,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3057,22 +3061,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124942395</v>
+        <v>124943491</v>
       </c>
       <c r="B23" t="n">
-        <v>96982</v>
+        <v>91023</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3085,38 +3089,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221946</v>
+        <v>1205</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597242</v>
+        <v>597211</v>
       </c>
       <c r="R23" t="n">
-        <v>6923954</v>
+        <v>6924014</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124941680</v>
+        <v>124943230</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,38 +1244,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597208</v>
+        <v>597393</v>
       </c>
       <c r="R7" t="n">
-        <v>6923937</v>
+        <v>6923922</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,22 +1337,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124943230</v>
+        <v>124941680</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,43 +1361,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597393</v>
+        <v>597208</v>
       </c>
       <c r="R8" t="n">
-        <v>6923922</v>
+        <v>6923937</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,12 +1449,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124944217</v>
+        <v>124941477</v>
       </c>
       <c r="B14" t="n">
-        <v>98124</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,38 +2053,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597242</v>
+        <v>597188</v>
       </c>
       <c r="R14" t="n">
-        <v>6923954</v>
+        <v>6923937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,22 +2141,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124941477</v>
+        <v>124943798</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,25 +2165,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2193,13 +2193,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597188</v>
+        <v>597302</v>
       </c>
       <c r="R15" t="n">
-        <v>6923937</v>
+        <v>6923956</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,22 +2253,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124943798</v>
+        <v>124944217</v>
       </c>
       <c r="B16" t="n">
-        <v>79795</v>
+        <v>98124</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,37 +2281,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597302</v>
+        <v>597242</v>
       </c>
       <c r="R16" t="n">
-        <v>6923956</v>
+        <v>6923954</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,12 +2365,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124652643</v>
+        <v>124655249</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,46 +808,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597090</v>
+        <v>597121</v>
       </c>
       <c r="R3" t="n">
-        <v>6924039</v>
+        <v>6924061</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124654038</v>
+        <v>124652643</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,43 +915,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597211</v>
+        <v>597090</v>
       </c>
       <c r="R4" t="n">
-        <v>6924014</v>
+        <v>6924039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +1013,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124655249</v>
+        <v>124653753</v>
       </c>
       <c r="B5" t="n">
         <v>57529</v>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597121</v>
+        <v>597211</v>
       </c>
       <c r="R5" t="n">
-        <v>6924061</v>
+        <v>6924014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124943440</v>
+        <v>124941126</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,34 +1136,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597242</v>
+        <v>597146</v>
       </c>
       <c r="R6" t="n">
-        <v>6923954</v>
+        <v>6923918</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1210,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,22 +1230,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124943230</v>
+        <v>124941477</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,43 +1254,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597393</v>
+        <v>597188</v>
       </c>
       <c r="R7" t="n">
-        <v>6923922</v>
+        <v>6923937</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,22 +1342,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124941680</v>
+        <v>124941736</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,34 +1370,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597208</v>
+        <v>597185</v>
       </c>
       <c r="R8" t="n">
-        <v>6923937</v>
+        <v>6923934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,19 +1454,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124944576</v>
+        <v>124942488</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1497,19 +1502,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597079</v>
+        <v>597356</v>
       </c>
       <c r="R9" t="n">
-        <v>6924029</v>
+        <v>6923925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,12 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,22 +1576,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124941910</v>
+        <v>124943798</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>79795</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,25 +1600,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597113</v>
+        <v>597302</v>
       </c>
       <c r="R10" t="n">
-        <v>6924130</v>
+        <v>6923956</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1695,7 +1700,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124941987</v>
+        <v>124942320</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1735,13 +1740,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597306</v>
+        <v>597221</v>
       </c>
       <c r="R11" t="n">
-        <v>6923901</v>
+        <v>6924056</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,7 +1775,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1785,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,22 +1800,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124941126</v>
+        <v>124941214</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,39 +1828,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597146</v>
+        <v>597182</v>
       </c>
       <c r="R12" t="n">
-        <v>6923918</v>
+        <v>6923894</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,12 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,22 +1912,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941214</v>
+        <v>124944217</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98124</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,38 +1936,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597182</v>
+        <v>597242</v>
       </c>
       <c r="R13" t="n">
-        <v>6923894</v>
+        <v>6923954</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +1999,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2009,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,22 +2024,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124941477</v>
+        <v>124941910</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,21 +2052,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,13 +2076,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597188</v>
+        <v>597113</v>
       </c>
       <c r="R14" t="n">
-        <v>6923937</v>
+        <v>6924130</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2116,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,22 +2136,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124943798</v>
+        <v>124941301</v>
       </c>
       <c r="B15" t="n">
-        <v>79795</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,37 +2164,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597302</v>
+        <v>597175</v>
       </c>
       <c r="R15" t="n">
-        <v>6923956</v>
+        <v>6923914</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,22 +2253,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124944217</v>
+        <v>124941987</v>
       </c>
       <c r="B16" t="n">
-        <v>98124</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597242</v>
+        <v>597306</v>
       </c>
       <c r="R16" t="n">
-        <v>6923954</v>
+        <v>6923901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,22 +2365,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124943857</v>
+        <v>124942008</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,39 +2393,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597272</v>
+        <v>597242</v>
       </c>
       <c r="R17" t="n">
-        <v>6923991</v>
+        <v>6923954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2467,7 +2462,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,22 +2477,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124941301</v>
+        <v>124942395</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>96982</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,27 +2505,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2539,10 +2533,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597175</v>
+        <v>597242</v>
       </c>
       <c r="R18" t="n">
-        <v>6923914</v>
+        <v>6923954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,22 +2593,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124942320</v>
+        <v>124943857</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,37 +2621,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597221</v>
+        <v>597272</v>
       </c>
       <c r="R19" t="n">
-        <v>6924056</v>
+        <v>6923991</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2686,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2695,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,22 +2710,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124942395</v>
+        <v>124941680</v>
       </c>
       <c r="B20" t="n">
-        <v>96982</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2735,42 +2734,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597242</v>
+        <v>597208</v>
       </c>
       <c r="R20" t="n">
-        <v>6923954</v>
+        <v>6923937</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,22 +2822,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124942488</v>
+        <v>124943491</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91023</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2851,43 +2846,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597356</v>
+        <v>597211</v>
       </c>
       <c r="R21" t="n">
-        <v>6923925</v>
+        <v>6924014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,7 +2909,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2929,12 +2919,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,10 +2946,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124941736</v>
+        <v>124943230</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2973,38 +2958,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597185</v>
+        <v>597393</v>
       </c>
       <c r="R22" t="n">
-        <v>6923934</v>
+        <v>6923922</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3046,7 +3036,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3073,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124943491</v>
+        <v>124944576</v>
       </c>
       <c r="B23" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3085,38 +3075,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597211</v>
+        <v>597079</v>
       </c>
       <c r="R23" t="n">
-        <v>6924014</v>
+        <v>6924029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,7 +3143,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,7 +3153,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124652643</v>
+        <v>124654038</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +915,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597090</v>
+        <v>597211</v>
       </c>
       <c r="R4" t="n">
-        <v>6924039</v>
+        <v>6924014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124653753</v>
+        <v>124652643</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,43 +1022,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597211</v>
+        <v>597090</v>
       </c>
       <c r="R5" t="n">
-        <v>6924014</v>
+        <v>6924039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124941477</v>
+        <v>124943230</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,38 +1254,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597188</v>
+        <v>597393</v>
       </c>
       <c r="R7" t="n">
-        <v>6923937</v>
+        <v>6923922</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,22 +1347,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124941736</v>
+        <v>124944576</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,34 +1375,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597185</v>
+        <v>597079</v>
       </c>
       <c r="R8" t="n">
-        <v>6923934</v>
+        <v>6924029</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1449,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,22 +1469,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124942488</v>
+        <v>124943857</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,16 +1497,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1507,14 +1522,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597356</v>
+        <v>597272</v>
       </c>
       <c r="R9" t="n">
-        <v>6923925</v>
+        <v>6923991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,22 +1586,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124943798</v>
+        <v>124944217</v>
       </c>
       <c r="B10" t="n">
-        <v>79795</v>
+        <v>98124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,37 +1614,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597302</v>
+        <v>597242</v>
       </c>
       <c r="R10" t="n">
-        <v>6923956</v>
+        <v>6923954</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,22 +1698,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124942320</v>
+        <v>124943798</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,25 +1722,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1740,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597221</v>
+        <v>597302</v>
       </c>
       <c r="R11" t="n">
-        <v>6924056</v>
+        <v>6923956</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1812,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124941214</v>
+        <v>124941680</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1852,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597182</v>
+        <v>597208</v>
       </c>
       <c r="R12" t="n">
-        <v>6923894</v>
+        <v>6923937</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,22 +1922,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124944217</v>
+        <v>124941214</v>
       </c>
       <c r="B13" t="n">
-        <v>98124</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,38 +1946,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597242</v>
+        <v>597182</v>
       </c>
       <c r="R13" t="n">
-        <v>6923954</v>
+        <v>6923894</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2009,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,12 +2034,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2148,10 +2158,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124941301</v>
+        <v>124942395</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>96982</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,27 +2174,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2193,10 +2202,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597175</v>
+        <v>597242</v>
       </c>
       <c r="R15" t="n">
-        <v>6923914</v>
+        <v>6923954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,19 +2262,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124941987</v>
+        <v>124942320</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2305,13 +2314,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597306</v>
+        <v>597221</v>
       </c>
       <c r="R16" t="n">
-        <v>6923901</v>
+        <v>6924056</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2340,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,22 +2374,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124942008</v>
+        <v>124941987</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,34 +2402,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597242</v>
+        <v>597306</v>
       </c>
       <c r="R17" t="n">
-        <v>6923954</v>
+        <v>6923901</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,22 +2486,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124942395</v>
+        <v>124942008</v>
       </c>
       <c r="B18" t="n">
-        <v>96982</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,32 +2510,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -2568,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2578,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2605,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124943857</v>
+        <v>124941301</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,43 +2622,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597272</v>
+        <v>597175</v>
       </c>
       <c r="R19" t="n">
-        <v>6923991</v>
+        <v>6923914</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2685,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,22 +2715,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124941680</v>
+        <v>124942488</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2738,34 +2743,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597208</v>
+        <v>597356</v>
       </c>
       <c r="R20" t="n">
-        <v>6923937</v>
+        <v>6923925</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2797,7 +2807,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2817,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,22 +2837,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124943491</v>
+        <v>124941736</v>
       </c>
       <c r="B21" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2846,38 +2861,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597211</v>
+        <v>597185</v>
       </c>
       <c r="R21" t="n">
-        <v>6924014</v>
+        <v>6923934</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,7 +2924,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2919,7 +2934,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2946,10 +2961,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124943230</v>
+        <v>124941477</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2958,43 +2973,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597393</v>
+        <v>597188</v>
       </c>
       <c r="R22" t="n">
-        <v>6923922</v>
+        <v>6923937</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3046,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,22 +3061,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124944576</v>
+        <v>124943491</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91023</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3075,43 +3085,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597079</v>
+        <v>597211</v>
       </c>
       <c r="R23" t="n">
-        <v>6924029</v>
+        <v>6924014</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3143,7 +3148,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3153,12 +3158,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124941126</v>
+        <v>124943230</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,20 +1132,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,19 +1156,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597146</v>
+        <v>597393</v>
       </c>
       <c r="R6" t="n">
-        <v>6923918</v>
+        <v>6923922</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,12 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,22 +1225,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124943230</v>
+        <v>124941126</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,20 +1249,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1278,19 +1273,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597393</v>
+        <v>597146</v>
       </c>
       <c r="R7" t="n">
-        <v>6923922</v>
+        <v>6923918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1327,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,12 +1347,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124942488</v>
+        <v>124941736</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2743,39 +2743,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597356</v>
+        <v>597185</v>
       </c>
       <c r="R20" t="n">
-        <v>6923925</v>
+        <v>6923934</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2807,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2817,12 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2849,10 +2839,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124941736</v>
+        <v>124942488</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,34 +2855,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597185</v>
+        <v>597356</v>
       </c>
       <c r="R21" t="n">
-        <v>6923934</v>
+        <v>6923925</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,7 +2919,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2934,7 +2929,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124655249</v>
+        <v>124654038</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597121</v>
+        <v>597211</v>
       </c>
       <c r="R3" t="n">
-        <v>6924061</v>
+        <v>6924014</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124654038</v>
+        <v>124655249</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597211</v>
+        <v>597121</v>
       </c>
       <c r="R4" t="n">
-        <v>6924014</v>
+        <v>6924061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124943230</v>
+        <v>124942395</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>96982</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,27 +1136,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1165,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597393</v>
+        <v>597242</v>
       </c>
       <c r="R6" t="n">
-        <v>6923922</v>
+        <v>6923954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,22 +1224,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124941126</v>
+        <v>124943440</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,39 +1252,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597146</v>
+        <v>597242</v>
       </c>
       <c r="R7" t="n">
-        <v>6923918</v>
+        <v>6923954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,12 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1336,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124944576</v>
+        <v>124941910</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,42 +1364,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597079</v>
+        <v>597113</v>
       </c>
       <c r="R8" t="n">
-        <v>6924029</v>
+        <v>6924130</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,12 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,22 +1448,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124943857</v>
+        <v>124942488</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,16 +1476,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1522,14 +1501,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597272</v>
+        <v>597356</v>
       </c>
       <c r="R9" t="n">
-        <v>6923991</v>
+        <v>6923925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1540,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1550,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,22 +1570,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124944217</v>
+        <v>124944576</v>
       </c>
       <c r="B10" t="n">
-        <v>98124</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,38 +1594,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597242</v>
+        <v>597079</v>
       </c>
       <c r="R10" t="n">
-        <v>6923954</v>
+        <v>6924029</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1672,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1692,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124943798</v>
+        <v>124942320</v>
       </c>
       <c r="B11" t="n">
-        <v>79795</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,25 +1716,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,10 +1744,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597302</v>
+        <v>597221</v>
       </c>
       <c r="R11" t="n">
-        <v>6923956</v>
+        <v>6924056</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1822,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124941680</v>
+        <v>124941301</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,38 +1828,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597208</v>
+        <v>597175</v>
       </c>
       <c r="R12" t="n">
-        <v>6923937</v>
+        <v>6923914</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,19 +1921,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941214</v>
+        <v>124941477</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1974,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597182</v>
+        <v>597188</v>
       </c>
       <c r="R13" t="n">
-        <v>6923894</v>
+        <v>6923937</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124941910</v>
+        <v>124943798</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>79795</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,25 +2057,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597113</v>
+        <v>597302</v>
       </c>
       <c r="R14" t="n">
-        <v>6924130</v>
+        <v>6923956</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2158,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124942395</v>
+        <v>124944217</v>
       </c>
       <c r="B15" t="n">
-        <v>96982</v>
+        <v>98124</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,28 +2173,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221946</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -2237,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124942320</v>
+        <v>124943491</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,41 +2281,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597221</v>
+        <v>597211</v>
       </c>
       <c r="R16" t="n">
-        <v>6924056</v>
+        <v>6924014</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2354,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,22 +2369,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124941987</v>
+        <v>124943230</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,38 +2393,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597306</v>
+        <v>597393</v>
       </c>
       <c r="R17" t="n">
-        <v>6923901</v>
+        <v>6923922</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,22 +2486,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124942008</v>
+        <v>124941736</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597242</v>
+        <v>597185</v>
       </c>
       <c r="R18" t="n">
-        <v>6923954</v>
+        <v>6923934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,22 +2598,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124941301</v>
+        <v>124943857</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,43 +2622,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597175</v>
+        <v>597272</v>
       </c>
       <c r="R19" t="n">
-        <v>6923914</v>
+        <v>6923991</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,22 +2715,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124941736</v>
+        <v>124941680</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2743,34 +2743,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597185</v>
+        <v>597208</v>
       </c>
       <c r="R20" t="n">
-        <v>6923934</v>
+        <v>6923937</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,22 +2827,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124942488</v>
+        <v>124941987</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,39 +2855,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597356</v>
+        <v>597306</v>
       </c>
       <c r="R21" t="n">
-        <v>6923925</v>
+        <v>6923901</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2929,12 +2924,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,22 +2939,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124941477</v>
+        <v>124941126</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2977,34 +2967,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597188</v>
+        <v>597146</v>
       </c>
       <c r="R22" t="n">
-        <v>6923937</v>
+        <v>6923918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,7 +3031,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3046,7 +3041,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,22 +3061,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124943491</v>
+        <v>124941214</v>
       </c>
       <c r="B23" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3085,38 +3085,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597211</v>
+        <v>597182</v>
       </c>
       <c r="R23" t="n">
-        <v>6924014</v>
+        <v>6923894</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124654038</v>
+        <v>124653753</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124942395</v>
+        <v>124943857</v>
       </c>
       <c r="B6" t="n">
-        <v>96982</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,42 +1132,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597242</v>
+        <v>597272</v>
       </c>
       <c r="R6" t="n">
-        <v>6923954</v>
+        <v>6923991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,22 +1225,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124943440</v>
+        <v>124941126</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,34 +1253,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597242</v>
+        <v>597146</v>
       </c>
       <c r="R7" t="n">
-        <v>6923954</v>
+        <v>6923918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1321,7 +1327,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,22 +1347,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124941910</v>
+        <v>124943798</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>79795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1371,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597113</v>
+        <v>597302</v>
       </c>
       <c r="R8" t="n">
-        <v>6924130</v>
+        <v>6923956</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1460,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124942488</v>
+        <v>124941214</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,39 +1487,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597356</v>
+        <v>597182</v>
       </c>
       <c r="R9" t="n">
-        <v>6923925</v>
+        <v>6923894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1550,12 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,22 +1571,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124944576</v>
+        <v>124944217</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>98124</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,43 +1595,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597079</v>
+        <v>597242</v>
       </c>
       <c r="R10" t="n">
-        <v>6924029</v>
+        <v>6923954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,12 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,22 +1683,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124942320</v>
+        <v>124942395</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>96982</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,41 +1707,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597221</v>
+        <v>597242</v>
       </c>
       <c r="R11" t="n">
-        <v>6924056</v>
+        <v>6923954</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1779,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1789,7 +1784,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,22 +1799,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124941301</v>
+        <v>124942320</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,46 +1823,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597175</v>
+        <v>597221</v>
       </c>
       <c r="R12" t="n">
-        <v>6923914</v>
+        <v>6924056</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1896,7 +1886,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1896,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,19 +1911,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941477</v>
+        <v>124941736</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1969,14 +1959,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597188</v>
+        <v>597185</v>
       </c>
       <c r="R13" t="n">
-        <v>6923937</v>
+        <v>6923934</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,22 +2023,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124943798</v>
+        <v>124943440</v>
       </c>
       <c r="B14" t="n">
-        <v>79795</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,41 +2047,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597302</v>
+        <v>597242</v>
       </c>
       <c r="R14" t="n">
-        <v>6923956</v>
+        <v>6923954</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2120,7 +2110,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2120,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,22 +2135,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124944217</v>
+        <v>124941680</v>
       </c>
       <c r="B15" t="n">
-        <v>98124</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,38 +2159,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597242</v>
+        <v>597208</v>
       </c>
       <c r="R15" t="n">
-        <v>6923954</v>
+        <v>6923937</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,22 +2247,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124943491</v>
+        <v>124941987</v>
       </c>
       <c r="B16" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,38 +2271,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597211</v>
+        <v>597306</v>
       </c>
       <c r="R16" t="n">
-        <v>6924014</v>
+        <v>6923901</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2334,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2344,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,22 +2359,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124943230</v>
+        <v>124941477</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,43 +2383,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597393</v>
+        <v>597188</v>
       </c>
       <c r="R17" t="n">
-        <v>6923922</v>
+        <v>6923937</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2456,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,22 +2471,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124941736</v>
+        <v>124941910</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,37 +2499,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597185</v>
+        <v>597113</v>
       </c>
       <c r="R18" t="n">
-        <v>6923934</v>
+        <v>6924130</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2573,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,22 +2583,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124943857</v>
+        <v>124942488</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,16 +2611,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2651,14 +2636,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597272</v>
+        <v>597356</v>
       </c>
       <c r="R19" t="n">
-        <v>6923991</v>
+        <v>6923925</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2685,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,22 +2705,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124941680</v>
+        <v>124944576</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2743,34 +2733,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597208</v>
+        <v>597079</v>
       </c>
       <c r="R20" t="n">
-        <v>6923937</v>
+        <v>6924029</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2807,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124941987</v>
+        <v>124943491</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2851,38 +2851,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597306</v>
+        <v>597211</v>
       </c>
       <c r="R21" t="n">
-        <v>6923901</v>
+        <v>6924014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,22 +2939,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124941126</v>
+        <v>124943230</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,20 +2963,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2987,19 +2987,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597146</v>
+        <v>597393</v>
       </c>
       <c r="R22" t="n">
-        <v>6923918</v>
+        <v>6923922</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3041,12 +3041,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,22 +3056,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124941214</v>
+        <v>124941301</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3085,38 +3080,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597182</v>
+        <v>597175</v>
       </c>
       <c r="R23" t="n">
-        <v>6923894</v>
+        <v>6923914</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124653753</v>
+        <v>124652643</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,43 +808,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597211</v>
+        <v>597090</v>
       </c>
       <c r="R3" t="n">
-        <v>6924014</v>
+        <v>6924039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655249</v>
+        <v>124654038</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -948,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597121</v>
+        <v>597211</v>
       </c>
       <c r="R4" t="n">
-        <v>6924061</v>
+        <v>6924014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652643</v>
+        <v>124655249</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,46 +1025,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597090</v>
+        <v>597121</v>
       </c>
       <c r="R5" t="n">
-        <v>6924039</v>
+        <v>6924061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124943857</v>
+        <v>124943440</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,39 +1136,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597272</v>
+        <v>597242</v>
       </c>
       <c r="R6" t="n">
-        <v>6923991</v>
+        <v>6923954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,22 +1220,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124941126</v>
+        <v>124941477</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,39 +1248,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597146</v>
+        <v>597188</v>
       </c>
       <c r="R7" t="n">
-        <v>6923918</v>
+        <v>6923937</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,12 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1332,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124943798</v>
+        <v>124943491</v>
       </c>
       <c r="B8" t="n">
-        <v>79795</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,37 +1360,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597302</v>
+        <v>597211</v>
       </c>
       <c r="R8" t="n">
-        <v>6923956</v>
+        <v>6924014</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,12 +1444,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1811,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124942320</v>
+        <v>124942488</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,37 +1812,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597221</v>
+        <v>597356</v>
       </c>
       <c r="R12" t="n">
-        <v>6924056</v>
+        <v>6923925</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,7 +1876,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,7 +1886,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,22 +1906,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941736</v>
+        <v>124941126</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,34 +1934,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597185</v>
+        <v>597146</v>
       </c>
       <c r="R13" t="n">
-        <v>6923934</v>
+        <v>6923918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,7 +2008,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,22 +2028,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124943440</v>
+        <v>124941987</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,34 +2056,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597242</v>
+        <v>597306</v>
       </c>
       <c r="R14" t="n">
-        <v>6923954</v>
+        <v>6923901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,7 +2115,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2120,7 +2125,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,22 +2140,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124941680</v>
+        <v>124943857</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2163,34 +2168,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597208</v>
+        <v>597272</v>
       </c>
       <c r="R15" t="n">
-        <v>6923937</v>
+        <v>6923991</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,19 +2257,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124941987</v>
+        <v>124941736</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2295,14 +2305,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597306</v>
+        <v>597185</v>
       </c>
       <c r="R16" t="n">
-        <v>6923901</v>
+        <v>6923934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2344,7 +2354,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,22 +2369,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124941477</v>
+        <v>124941680</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,21 +2397,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2411,7 +2421,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597188</v>
+        <v>597208</v>
       </c>
       <c r="R17" t="n">
         <v>6923937</v>
@@ -2471,22 +2481,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124941910</v>
+        <v>124942320</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,21 +2509,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2523,10 +2533,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597113</v>
+        <v>597221</v>
       </c>
       <c r="R18" t="n">
-        <v>6924130</v>
+        <v>6924056</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2595,10 +2605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124942488</v>
+        <v>124941910</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2611,42 +2621,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597356</v>
+        <v>597113</v>
       </c>
       <c r="R19" t="n">
-        <v>6923925</v>
+        <v>6924130</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2675,7 +2680,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2685,12 +2690,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,22 +2705,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124944576</v>
+        <v>124941301</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,43 +2729,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597079</v>
+        <v>597175</v>
       </c>
       <c r="R20" t="n">
-        <v>6924029</v>
+        <v>6923914</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,12 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,22 +2822,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124943491</v>
+        <v>124943798</v>
       </c>
       <c r="B21" t="n">
-        <v>91023</v>
+        <v>79795</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,37 +2850,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597211</v>
+        <v>597302</v>
       </c>
       <c r="R21" t="n">
-        <v>6924014</v>
+        <v>6923956</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2914,7 +2909,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2919,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,12 +2934,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3068,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124941301</v>
+        <v>124944576</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3080,43 +3075,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597175</v>
+        <v>597079</v>
       </c>
       <c r="R23" t="n">
-        <v>6923914</v>
+        <v>6924029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,7 +3143,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,7 +3153,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124652643</v>
+        <v>124653753</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,46 +808,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597090</v>
+        <v>597211</v>
       </c>
       <c r="R3" t="n">
-        <v>6924039</v>
+        <v>6924014</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124654038</v>
+        <v>124655249</v>
       </c>
       <c r="B4" t="n">
         <v>57529</v>
@@ -951,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597211</v>
+        <v>597121</v>
       </c>
       <c r="R4" t="n">
-        <v>6924014</v>
+        <v>6924061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124655249</v>
+        <v>124652643</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,43 +1022,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597121</v>
+        <v>597090</v>
       </c>
       <c r="R5" t="n">
-        <v>6924061</v>
+        <v>6924039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2834,10 +2834,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124943798</v>
+        <v>124943230</v>
       </c>
       <c r="B21" t="n">
-        <v>79795</v>
+        <v>57883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2850,37 +2850,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597302</v>
+        <v>597393</v>
       </c>
       <c r="R21" t="n">
-        <v>6923956</v>
+        <v>6923922</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2909,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2919,7 +2924,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,22 +2939,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124943230</v>
+        <v>124943798</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>79795</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2962,42 +2967,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597393</v>
+        <v>597302</v>
       </c>
       <c r="R22" t="n">
-        <v>6923922</v>
+        <v>6923956</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,12 +3051,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124943440</v>
+        <v>124944576</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,34 +1136,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597242</v>
+        <v>597079</v>
       </c>
       <c r="R6" t="n">
-        <v>6923954</v>
+        <v>6924029</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1210,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,12 +1230,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1344,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124943491</v>
+        <v>124941987</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,38 +1366,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597211</v>
+        <v>597306</v>
       </c>
       <c r="R8" t="n">
-        <v>6924014</v>
+        <v>6923901</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,22 +1454,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124941214</v>
+        <v>124942488</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,34 +1482,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597182</v>
+        <v>597356</v>
       </c>
       <c r="R9" t="n">
-        <v>6923894</v>
+        <v>6923925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1541,7 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,22 +1576,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124944217</v>
+        <v>124942320</v>
       </c>
       <c r="B10" t="n">
-        <v>98124</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,41 +1600,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597242</v>
+        <v>597221</v>
       </c>
       <c r="R10" t="n">
-        <v>6923954</v>
+        <v>6924056</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1653,7 +1673,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,22 +1688,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124942395</v>
+        <v>124943440</v>
       </c>
       <c r="B11" t="n">
-        <v>96982</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,32 +1712,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -1759,7 +1775,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1785,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124942488</v>
+        <v>124941680</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,39 +1828,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597356</v>
+        <v>597208</v>
       </c>
       <c r="R12" t="n">
-        <v>6923925</v>
+        <v>6923937</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1886,12 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,22 +1912,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941126</v>
+        <v>124941910</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,42 +1940,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597146</v>
+        <v>597113</v>
       </c>
       <c r="R13" t="n">
-        <v>6923918</v>
+        <v>6924130</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1998,7 +1999,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +2009,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,22 +2024,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124941987</v>
+        <v>124943230</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2052,38 +2048,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597306</v>
+        <v>597393</v>
       </c>
       <c r="R14" t="n">
-        <v>6923901</v>
+        <v>6923922</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2125,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,22 +2141,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124943857</v>
+        <v>124941126</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,16 +2169,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2197,10 +2198,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597272</v>
+        <v>597146</v>
       </c>
       <c r="R15" t="n">
-        <v>6923991</v>
+        <v>6923918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2243,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,22 +2263,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124941736</v>
+        <v>124943798</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>79795</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,41 +2287,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597185</v>
+        <v>597302</v>
       </c>
       <c r="R16" t="n">
-        <v>6923934</v>
+        <v>6923956</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2344,7 +2350,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2360,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,22 +2375,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124941680</v>
+        <v>124941736</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,34 +2403,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597208</v>
+        <v>597185</v>
       </c>
       <c r="R17" t="n">
-        <v>6923937</v>
+        <v>6923934</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,7 +2462,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2466,7 +2472,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,19 +2487,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124942320</v>
+        <v>124941214</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2533,13 +2539,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597221</v>
+        <v>597182</v>
       </c>
       <c r="R18" t="n">
-        <v>6924056</v>
+        <v>6923894</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2568,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2578,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,22 +2599,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124941910</v>
+        <v>124944217</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>98124</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,41 +2623,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597113</v>
+        <v>597242</v>
       </c>
       <c r="R19" t="n">
-        <v>6924130</v>
+        <v>6923954</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2680,7 +2686,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2690,7 +2696,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,22 +2711,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124941301</v>
+        <v>124943491</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>91023</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2733,39 +2739,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597175</v>
+        <v>597211</v>
       </c>
       <c r="R20" t="n">
-        <v>6923914</v>
+        <v>6924014</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2797,7 +2798,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2808,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,10 +2835,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124943230</v>
+        <v>124942395</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>96982</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2850,27 +2851,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597393</v>
+        <v>597242</v>
       </c>
       <c r="R21" t="n">
-        <v>6923922</v>
+        <v>6923954</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,22 +2939,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124943798</v>
+        <v>124941301</v>
       </c>
       <c r="B22" t="n">
-        <v>79795</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2967,37 +2967,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597302</v>
+        <v>597175</v>
       </c>
       <c r="R22" t="n">
-        <v>6923956</v>
+        <v>6923914</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3026,7 +3031,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3041,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,22 +3056,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124944576</v>
+        <v>124943857</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,16 +3084,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3099,7 +3104,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597079</v>
+        <v>597272</v>
       </c>
       <c r="R23" t="n">
-        <v>6924029</v>
+        <v>6923991</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3143,7 +3148,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3153,12 +3158,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124653753</v>
+        <v>124654038</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655249</v>
+        <v>124652643</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,43 +915,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597121</v>
+        <v>597090</v>
       </c>
       <c r="R4" t="n">
-        <v>6924061</v>
+        <v>6924039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652643</v>
+        <v>124655249</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,46 +1025,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597090</v>
+        <v>597121</v>
       </c>
       <c r="R5" t="n">
-        <v>6924039</v>
+        <v>6924061</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124944576</v>
+        <v>124941680</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,39 +1136,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597079</v>
+        <v>597208</v>
       </c>
       <c r="R6" t="n">
-        <v>6924029</v>
+        <v>6923937</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,12 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124941477</v>
+        <v>124944217</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98124</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,38 +1244,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597188</v>
+        <v>597242</v>
       </c>
       <c r="R7" t="n">
-        <v>6923937</v>
+        <v>6923954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,19 +1332,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124941987</v>
+        <v>124941736</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1390,14 +1380,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597306</v>
+        <v>597185</v>
       </c>
       <c r="R8" t="n">
-        <v>6923901</v>
+        <v>6923934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,22 +1444,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124942488</v>
+        <v>124943230</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,20 +1468,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1502,7 +1492,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1511,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597356</v>
+        <v>597393</v>
       </c>
       <c r="R9" t="n">
-        <v>6923925</v>
+        <v>6923922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1546,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1700,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124943440</v>
+        <v>124944576</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,34 +1701,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597242</v>
+        <v>597079</v>
       </c>
       <c r="R11" t="n">
-        <v>6923954</v>
+        <v>6924029</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1775,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,19 +1795,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124941680</v>
+        <v>124943440</v>
       </c>
       <c r="B12" t="n">
         <v>79891</v>
@@ -1848,14 +1843,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597208</v>
+        <v>597242</v>
       </c>
       <c r="R12" t="n">
-        <v>6923937</v>
+        <v>6923954</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,22 +1907,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941910</v>
+        <v>124941987</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,21 +1935,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1964,13 +1959,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597113</v>
+        <v>597306</v>
       </c>
       <c r="R13" t="n">
-        <v>6924130</v>
+        <v>6923901</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,7 +1994,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2009,7 +2004,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,22 +2019,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124943230</v>
+        <v>124943857</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,20 +2043,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2072,19 +2067,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597393</v>
+        <v>597272</v>
       </c>
       <c r="R14" t="n">
-        <v>6923922</v>
+        <v>6923991</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,19 +2136,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124941126</v>
+        <v>124942488</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2194,14 +2189,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597146</v>
+        <v>597356</v>
       </c>
       <c r="R15" t="n">
-        <v>6923918</v>
+        <v>6923925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2243,12 +2238,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,22 +2258,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124943798</v>
+        <v>124942395</v>
       </c>
       <c r="B16" t="n">
-        <v>79795</v>
+        <v>96982</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,37 +2286,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>221946</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597302</v>
+        <v>597242</v>
       </c>
       <c r="R16" t="n">
-        <v>6923956</v>
+        <v>6923954</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2350,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2360,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,22 +2374,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124941736</v>
+        <v>124943491</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,38 +2398,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597185</v>
+        <v>597211</v>
       </c>
       <c r="R17" t="n">
-        <v>6923934</v>
+        <v>6924014</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2462,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2472,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2611,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124944217</v>
+        <v>124941910</v>
       </c>
       <c r="B19" t="n">
-        <v>98124</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2623,41 +2622,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597242</v>
+        <v>597113</v>
       </c>
       <c r="R19" t="n">
-        <v>6923954</v>
+        <v>6924130</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2686,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2696,7 +2695,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,22 +2710,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124943491</v>
+        <v>124943798</v>
       </c>
       <c r="B20" t="n">
-        <v>91023</v>
+        <v>79795</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2739,37 +2738,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1205</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597211</v>
+        <v>597302</v>
       </c>
       <c r="R20" t="n">
-        <v>6924014</v>
+        <v>6923956</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2798,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2808,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,22 +2822,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124942395</v>
+        <v>124941126</v>
       </c>
       <c r="B21" t="n">
-        <v>96982</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2847,42 +2846,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597242</v>
+        <v>597146</v>
       </c>
       <c r="R21" t="n">
-        <v>6923954</v>
+        <v>6923918</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2924,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,22 +2944,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124941301</v>
+        <v>124941477</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,43 +2968,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597175</v>
+        <v>597188</v>
       </c>
       <c r="R22" t="n">
-        <v>6923914</v>
+        <v>6923937</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3056,22 +3056,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124943857</v>
+        <v>124941301</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3080,43 +3080,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597272</v>
+        <v>597175</v>
       </c>
       <c r="R23" t="n">
-        <v>6923991</v>
+        <v>6923914</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>124654038</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124652643</v>
+        <v>124655249</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +915,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597090</v>
+        <v>597121</v>
       </c>
       <c r="R4" t="n">
-        <v>6924039</v>
+        <v>6924061</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124655249</v>
+        <v>124652643</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,43 +1022,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Tjäder, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597121</v>
+        <v>597090</v>
       </c>
       <c r="R5" t="n">
-        <v>6924061</v>
+        <v>6924039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124941680</v>
+        <v>124943798</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79932</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1132,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597208</v>
+        <v>597302</v>
       </c>
       <c r="R6" t="n">
-        <v>6923937</v>
+        <v>6923956</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,22 +1220,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124944217</v>
+        <v>124941680</v>
       </c>
       <c r="B7" t="n">
-        <v>98124</v>
+        <v>80028</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,38 +1244,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597242</v>
+        <v>597208</v>
       </c>
       <c r="R7" t="n">
-        <v>6923954</v>
+        <v>6923937</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,22 +1332,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124941736</v>
+        <v>124943230</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>58001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,38 +1356,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597185</v>
+        <v>597393</v>
       </c>
       <c r="R8" t="n">
-        <v>6923934</v>
+        <v>6923922</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124943230</v>
+        <v>124941477</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,43 +1473,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597393</v>
+        <v>597188</v>
       </c>
       <c r="R9" t="n">
-        <v>6923922</v>
+        <v>6923937</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,22 +1561,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124942320</v>
+        <v>124942395</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>97150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,41 +1585,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597221</v>
+        <v>597242</v>
       </c>
       <c r="R10" t="n">
-        <v>6924056</v>
+        <v>6923954</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1658,7 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,22 +1677,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124944576</v>
+        <v>124942320</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,42 +1705,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597079</v>
+        <v>597221</v>
       </c>
       <c r="R11" t="n">
-        <v>6924029</v>
+        <v>6924056</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,7 +1764,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,12 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,22 +1789,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124943440</v>
+        <v>124943857</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,34 +1817,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597242</v>
+        <v>597272</v>
       </c>
       <c r="R12" t="n">
-        <v>6923954</v>
+        <v>6923991</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1881,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1891,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,22 +1906,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941987</v>
+        <v>124941910</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91116</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,21 +1934,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,13 +1958,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597306</v>
+        <v>597113</v>
       </c>
       <c r="R13" t="n">
-        <v>6923901</v>
+        <v>6924130</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2004,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,22 +2018,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124943857</v>
+        <v>124943491</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>91177</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,43 +2042,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597272</v>
+        <v>597211</v>
       </c>
       <c r="R14" t="n">
-        <v>6923991</v>
+        <v>6924014</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2105,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2115,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,22 +2130,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124942488</v>
+        <v>124941126</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,14 +2183,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597356</v>
+        <v>597146</v>
       </c>
       <c r="R15" t="n">
-        <v>6923925</v>
+        <v>6923918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,12 +2232,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack gran.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,22 +2252,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124942395</v>
+        <v>124943440</v>
       </c>
       <c r="B16" t="n">
-        <v>96982</v>
+        <v>80028</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,32 +2276,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221946</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
@@ -2349,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124943491</v>
+        <v>124941214</v>
       </c>
       <c r="B17" t="n">
-        <v>91023</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,38 +2388,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597211</v>
+        <v>597182</v>
       </c>
       <c r="R17" t="n">
-        <v>6924014</v>
+        <v>6923894</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,22 +2476,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124941214</v>
+        <v>124941987</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,10 +2528,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597182</v>
+        <v>597306</v>
       </c>
       <c r="R18" t="n">
-        <v>6923894</v>
+        <v>6923901</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2563,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2573,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,10 +2600,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124941910</v>
+        <v>124941301</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>56836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2622,41 +2612,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597113</v>
+        <v>597175</v>
       </c>
       <c r="R19" t="n">
-        <v>6924130</v>
+        <v>6923914</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2685,7 +2680,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,7 +2690,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,22 +2705,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124943798</v>
+        <v>124944217</v>
       </c>
       <c r="B20" t="n">
-        <v>79795</v>
+        <v>98292</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2738,37 +2733,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597302</v>
+        <v>597242</v>
       </c>
       <c r="R20" t="n">
-        <v>6923956</v>
+        <v>6923954</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2797,7 +2792,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2802,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,22 +2817,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124941126</v>
+        <v>124942488</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2875,14 +2870,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597146</v>
+        <v>597356</v>
       </c>
       <c r="R21" t="n">
-        <v>6923918</v>
+        <v>6923925</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2909,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,12 +2919,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2944,22 +2939,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124941477</v>
+        <v>124941736</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2992,14 +2987,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597188</v>
+        <v>597185</v>
       </c>
       <c r="R22" t="n">
-        <v>6923937</v>
+        <v>6923934</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3041,7 +3036,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3056,22 +3051,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124941301</v>
+        <v>124944576</v>
       </c>
       <c r="B23" t="n">
-        <v>56722</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3080,43 +3075,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597175</v>
+        <v>597079</v>
       </c>
       <c r="R23" t="n">
-        <v>6923914</v>
+        <v>6924029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,7 +3143,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,7 +3153,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124943798</v>
+        <v>124942320</v>
       </c>
       <c r="B6" t="n">
-        <v>79932</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,25 +1132,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597302</v>
+        <v>597221</v>
       </c>
       <c r="R6" t="n">
-        <v>6923956</v>
+        <v>6924056</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124941680</v>
+        <v>124941987</v>
       </c>
       <c r="B7" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597208</v>
+        <v>597306</v>
       </c>
       <c r="R7" t="n">
-        <v>6923937</v>
+        <v>6923901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,22 +1332,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124943230</v>
+        <v>124942395</v>
       </c>
       <c r="B8" t="n">
-        <v>58001</v>
+        <v>97150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,27 +1360,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1389,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597393</v>
+        <v>597242</v>
       </c>
       <c r="R8" t="n">
-        <v>6923922</v>
+        <v>6923954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,22 +1448,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124941477</v>
+        <v>124941910</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>91116</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,21 +1476,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,13 +1500,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597188</v>
+        <v>597113</v>
       </c>
       <c r="R9" t="n">
-        <v>6923937</v>
+        <v>6924130</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,7 +1545,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,22 +1560,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124942395</v>
+        <v>124942488</v>
       </c>
       <c r="B10" t="n">
-        <v>97150</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,30 +1584,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597242</v>
+        <v>597356</v>
       </c>
       <c r="R10" t="n">
-        <v>6923954</v>
+        <v>6923925</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,7 +1662,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,22 +1682,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124942320</v>
+        <v>124943857</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,37 +1710,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597221</v>
+        <v>597272</v>
       </c>
       <c r="R11" t="n">
-        <v>6924056</v>
+        <v>6923991</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1774,7 +1784,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1789,22 +1799,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124943857</v>
+        <v>124943440</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,39 +1827,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597272</v>
+        <v>597242</v>
       </c>
       <c r="R12" t="n">
-        <v>6923991</v>
+        <v>6923954</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,7 +1886,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,7 +1896,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,22 +1911,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941910</v>
+        <v>124943491</v>
       </c>
       <c r="B13" t="n">
-        <v>91116</v>
+        <v>91177</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,41 +1935,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597113</v>
+        <v>597211</v>
       </c>
       <c r="R13" t="n">
-        <v>6924130</v>
+        <v>6924014</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1993,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,22 +2023,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124943491</v>
+        <v>124941214</v>
       </c>
       <c r="B14" t="n">
-        <v>91177</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2042,38 +2047,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597211</v>
+        <v>597182</v>
       </c>
       <c r="R14" t="n">
-        <v>6924014</v>
+        <v>6923894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2105,7 +2110,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2115,7 +2120,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,22 +2135,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124941126</v>
+        <v>124944217</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
+        <v>98292</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2154,43 +2159,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597146</v>
+        <v>597242</v>
       </c>
       <c r="R15" t="n">
-        <v>6923918</v>
+        <v>6923954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,12 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,22 +2247,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124943440</v>
+        <v>124941736</v>
       </c>
       <c r="B16" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2304,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597242</v>
+        <v>597185</v>
       </c>
       <c r="R16" t="n">
-        <v>6923954</v>
+        <v>6923934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,7 +2334,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2349,7 +2344,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,22 +2359,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124941214</v>
+        <v>124941126</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,34 +2387,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597182</v>
+        <v>597146</v>
       </c>
       <c r="R17" t="n">
-        <v>6923894</v>
+        <v>6923918</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2461,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,22 +2481,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124941987</v>
+        <v>124943798</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
+        <v>79932</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,25 +2505,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2528,13 +2533,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597306</v>
+        <v>597302</v>
       </c>
       <c r="R18" t="n">
-        <v>6923901</v>
+        <v>6923956</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2573,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,22 +2593,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124941301</v>
+        <v>124941680</v>
       </c>
       <c r="B19" t="n">
-        <v>56836</v>
+        <v>80028</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,43 +2617,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597175</v>
+        <v>597208</v>
       </c>
       <c r="R19" t="n">
-        <v>6923914</v>
+        <v>6923937</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,22 +2705,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124944217</v>
+        <v>124944576</v>
       </c>
       <c r="B20" t="n">
-        <v>98292</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,38 +2729,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597242</v>
+        <v>597079</v>
       </c>
       <c r="R20" t="n">
-        <v>6923954</v>
+        <v>6924029</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2792,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2802,7 +2807,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,22 +2827,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124942488</v>
+        <v>124941301</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,31 +2851,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2874,10 +2884,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597356</v>
+        <v>597175</v>
       </c>
       <c r="R21" t="n">
-        <v>6923925</v>
+        <v>6923914</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,7 +2919,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2919,12 +2929,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2951,10 +2956,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124941736</v>
+        <v>124943230</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>58001</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,38 +2968,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597185</v>
+        <v>597393</v>
       </c>
       <c r="R22" t="n">
-        <v>6923934</v>
+        <v>6923922</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3046,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,10 +3073,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124944576</v>
+        <v>124941477</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,39 +3089,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597079</v>
+        <v>597188</v>
       </c>
       <c r="R23" t="n">
-        <v>6924029</v>
+        <v>6923937</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3143,7 +3148,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3153,12 +3158,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124944576</v>
+        <v>124943230</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
+        <v>58001</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,20 +2729,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2753,19 +2753,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597079</v>
+        <v>597393</v>
       </c>
       <c r="R20" t="n">
-        <v>6924029</v>
+        <v>6923922</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,12 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,22 +2822,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124941301</v>
+        <v>124944576</v>
       </c>
       <c r="B21" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2851,43 +2846,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597175</v>
+        <v>597079</v>
       </c>
       <c r="R21" t="n">
-        <v>6923914</v>
+        <v>6924029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2929,7 +2924,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2944,22 +2944,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124943230</v>
+        <v>124941301</v>
       </c>
       <c r="B22" t="n">
-        <v>58001</v>
+        <v>56836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2972,27 +2972,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597393</v>
+        <v>597175</v>
       </c>
       <c r="R22" t="n">
-        <v>6923922</v>
+        <v>6923914</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -1120,15 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124942320</v>
+        <v>124944576</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,37 +1131,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597221</v>
+        <v>597079</v>
       </c>
       <c r="R6" t="n">
-        <v>6924056</v>
+        <v>6924029</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,62 +1225,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124941987</v>
+        <v>124942395</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597306</v>
+        <v>597242</v>
       </c>
       <c r="R7" t="n">
-        <v>6923901</v>
+        <v>6923954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1311,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1321,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,27 +1336,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124942395</v>
+        <v>124943230</v>
       </c>
       <c r="B8" t="n">
-        <v>97150</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58001</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,26 +1359,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597242</v>
+        <v>597393</v>
       </c>
       <c r="R8" t="n">
-        <v>6923954</v>
+        <v>6923922</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,27 +1448,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124941910</v>
+        <v>124942488</v>
       </c>
       <c r="B9" t="n">
-        <v>91116</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,37 +1471,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597113</v>
+        <v>597356</v>
       </c>
       <c r="R9" t="n">
-        <v>6924130</v>
+        <v>6923925</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,7 +1545,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,27 +1565,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124942488</v>
+        <v>124943857</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,16 +1588,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1613,14 +1613,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597356</v>
+        <v>597272</v>
       </c>
       <c r="R10" t="n">
-        <v>6923925</v>
+        <v>6923991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1662,12 +1662,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,27 +1677,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124943857</v>
+        <v>124941477</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,39 +1700,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597272</v>
+        <v>597188</v>
       </c>
       <c r="R11" t="n">
-        <v>6923991</v>
+        <v>6923937</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,7 +1759,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,7 +1769,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,15 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124943440</v>
+        <v>124942320</v>
       </c>
       <c r="B12" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,37 +1807,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597242</v>
+        <v>597221</v>
       </c>
       <c r="R12" t="n">
-        <v>6923954</v>
+        <v>6924056</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,7 +1866,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,7 +1876,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,65 +1891,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124943491</v>
+        <v>124941910</v>
       </c>
       <c r="B13" t="n">
-        <v>91177</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597211</v>
+        <v>597113</v>
       </c>
       <c r="R13" t="n">
-        <v>6924014</v>
+        <v>6924130</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1998,7 +1973,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,7 +1983,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,62 +1998,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124941214</v>
+        <v>124944217</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597182</v>
+        <v>597242</v>
       </c>
       <c r="R14" t="n">
-        <v>6923894</v>
+        <v>6923954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,7 +2080,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2120,7 +2090,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,62 +2105,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124944217</v>
+        <v>124941680</v>
       </c>
       <c r="B15" t="n">
-        <v>98292</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597242</v>
+        <v>597208</v>
       </c>
       <c r="R15" t="n">
-        <v>6923954</v>
+        <v>6923937</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,7 +2187,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2232,7 +2197,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,62 +2212,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124941736</v>
+        <v>124943491</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597185</v>
+        <v>597211</v>
       </c>
       <c r="R16" t="n">
-        <v>6923934</v>
+        <v>6924014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2294,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2344,7 +2304,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,15 +2331,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124941126</v>
+        <v>124941214</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,39 +2342,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597146</v>
+        <v>597182</v>
       </c>
       <c r="R17" t="n">
-        <v>6923918</v>
+        <v>6923894</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2401,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,12 +2411,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,27 +2426,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124943798</v>
+        <v>124941301</v>
       </c>
       <c r="B18" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,37 +2449,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597302</v>
+        <v>597175</v>
       </c>
       <c r="R18" t="n">
-        <v>6923956</v>
+        <v>6923914</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2568,7 +2513,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2578,7 +2523,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,49 +2538,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124941680</v>
+        <v>124943798</v>
       </c>
       <c r="B19" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79932</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2645,13 +2585,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597208</v>
+        <v>597302</v>
       </c>
       <c r="R19" t="n">
-        <v>6923937</v>
+        <v>6923956</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2680,7 +2620,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2690,7 +2630,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,67 +2645,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124943230</v>
+        <v>124941736</v>
       </c>
       <c r="B20" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597393</v>
+        <v>597185</v>
       </c>
       <c r="R20" t="n">
-        <v>6923922</v>
+        <v>6923934</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2797,7 +2727,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2737,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,16 +2764,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124944576</v>
+        <v>124941126</v>
       </c>
       <c r="B21" t="n">
         <v>57635</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2870,7 +2795,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2879,10 +2804,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597079</v>
+        <v>597146</v>
       </c>
       <c r="R21" t="n">
-        <v>6924029</v>
+        <v>6923918</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2839,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2849,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2956,55 +2881,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124941301</v>
+        <v>124943440</v>
       </c>
       <c r="B22" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597175</v>
+        <v>597242</v>
       </c>
       <c r="R22" t="n">
-        <v>6923914</v>
+        <v>6923954</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,7 +2951,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3046,7 +2961,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,28 +2976,23 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124941477</v>
+        <v>124941987</v>
       </c>
       <c r="B23" t="n">
         <v>78947</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3113,10 +3023,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597188</v>
+        <v>597306</v>
       </c>
       <c r="R23" t="n">
-        <v>6923937</v>
+        <v>6923901</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,7 +3058,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,7 +3068,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -799,12 +799,7 @@
         <v>124654038</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,12 +901,7 @@
         <v>124655249</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1580,7 +1570,7 @@
         <v>124943857</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>124654038</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>124655249</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>124943857</v>
       </c>
       <c r="B10" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>124654038</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>124655249</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>124943857</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>124654038</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>124655249</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>124943857</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>124654038</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>124655249</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>124943857</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>124654038</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>124655249</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>124943857</v>
       </c>
       <c r="B10" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>124944576</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>124942488</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>124941126</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>124944576</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>124942488</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>124941126</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,72 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124426368</v>
+        <v>124941910</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597061</v>
+        <v>597113</v>
       </c>
       <c r="R2" t="n">
-        <v>6924025</v>
+        <v>6924130</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,52 +770,47 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124654038</v>
+        <v>124943491</v>
       </c>
       <c r="B3" t="n">
-        <v>57681</v>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spillkråka, Mpd</t>
@@ -866,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124655249</v>
+        <v>124941214</v>
       </c>
       <c r="B4" t="n">
-        <v>57681</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597121</v>
+        <v>597182</v>
       </c>
       <c r="R4" t="n">
-        <v>6924061</v>
+        <v>6923894</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,12 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,70 +984,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124652643</v>
+        <v>124941477</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjäder, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597090</v>
+        <v>597188</v>
       </c>
       <c r="R5" t="n">
-        <v>6924039</v>
+        <v>6923937</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,12 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,62 +1091,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124944576</v>
+        <v>124941736</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597079</v>
+        <v>597185</v>
       </c>
       <c r="R6" t="n">
-        <v>6924029</v>
+        <v>6923934</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,12 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:34</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,61 +1198,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124942395</v>
+        <v>124941987</v>
       </c>
       <c r="B7" t="n">
-        <v>97150</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597242</v>
+        <v>597306</v>
       </c>
       <c r="R7" t="n">
-        <v>6923954</v>
+        <v>6923901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1311,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,65 +1305,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124943230</v>
+        <v>124942320</v>
       </c>
       <c r="B8" t="n">
-        <v>58001</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597393</v>
+        <v>597221</v>
       </c>
       <c r="R8" t="n">
-        <v>6923922</v>
+        <v>6924056</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,65 +1412,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124942488</v>
+        <v>124943247</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597356</v>
+        <v>597400</v>
       </c>
       <c r="R9" t="n">
-        <v>6923925</v>
+        <v>6923927</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack gran.</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,62 +1519,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124943857</v>
+        <v>124943420</v>
       </c>
       <c r="B10" t="n">
-        <v>57681</v>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597272</v>
+        <v>597410</v>
       </c>
       <c r="R10" t="n">
-        <v>6923991</v>
+        <v>6923958</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1652,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,44 +1626,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124941477</v>
+        <v>124943672</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>80336</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597188</v>
+        <v>597339</v>
       </c>
       <c r="R11" t="n">
-        <v>6923937</v>
+        <v>6924019</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,44 +1733,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124942320</v>
+        <v>124943798</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1821,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597221</v>
+        <v>597302</v>
       </c>
       <c r="R12" t="n">
-        <v>6924056</v>
+        <v>6923956</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1893,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124941910</v>
+        <v>124941680</v>
       </c>
       <c r="B13" t="n">
-        <v>91116</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1928,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597113</v>
+        <v>597208</v>
       </c>
       <c r="R13" t="n">
-        <v>6924130</v>
+        <v>6923937</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1963,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,57 +1947,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124944217</v>
+        <v>124941845</v>
       </c>
       <c r="B14" t="n">
-        <v>98292</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597242</v>
+        <v>597262</v>
       </c>
       <c r="R14" t="n">
-        <v>6923954</v>
+        <v>6923873</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2080,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,22 +2054,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124941680</v>
+        <v>124942008</v>
       </c>
       <c r="B15" t="n">
-        <v>80028</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,14 +2097,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597208</v>
+        <v>597242</v>
       </c>
       <c r="R15" t="n">
-        <v>6923937</v>
+        <v>6923954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2187,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2202,57 +2161,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124943491</v>
+        <v>124943160</v>
       </c>
       <c r="B16" t="n">
-        <v>91177</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Spillkråka, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597211</v>
+        <v>597397</v>
       </c>
       <c r="R16" t="n">
-        <v>6924014</v>
+        <v>6923917</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2284,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2294,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2309,57 +2268,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124941214</v>
+        <v>124653753</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597182</v>
+        <v>597211</v>
       </c>
       <c r="R17" t="n">
-        <v>6923894</v>
+        <v>6924014</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,22 +2350,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>18:12</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>18:12</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,22 +2370,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124941301</v>
+        <v>124655249</v>
       </c>
       <c r="B18" t="n">
-        <v>56836</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,39 +2393,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Spillkråka, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597175</v>
+        <v>597121</v>
       </c>
       <c r="R18" t="n">
-        <v>6923914</v>
+        <v>6924061</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2498,22 +2452,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>18:08</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>18:08</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2540,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124943798</v>
+        <v>124943857</v>
       </c>
       <c r="B19" t="n">
-        <v>79932</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,37 +2495,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597302</v>
+        <v>597272</v>
       </c>
       <c r="R19" t="n">
-        <v>6923956</v>
+        <v>6923991</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,7 +2559,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2620,7 +2569,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,57 +2584,62 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124941736</v>
+        <v>124943977</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597185</v>
+        <v>597266</v>
       </c>
       <c r="R20" t="n">
-        <v>6923934</v>
+        <v>6924021</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2727,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2742,39 +2696,39 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124941126</v>
+        <v>124944043</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2794,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597146</v>
+        <v>597236</v>
       </c>
       <c r="R21" t="n">
-        <v>6923918</v>
+        <v>6924044</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2829,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2839,12 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2859,22 +2808,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124943440</v>
+        <v>124941126</v>
       </c>
       <c r="B22" t="n">
-        <v>80028</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2882,34 +2831,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Himmelsmyran, Mpd</t>
+          <t>Oxmyran, Oxmyran, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597242</v>
+        <v>597146</v>
       </c>
       <c r="R22" t="n">
-        <v>6923954</v>
+        <v>6923918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2941,7 +2895,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2951,7 +2905,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2966,22 +2925,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124941987</v>
+        <v>124942488</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2989,34 +2948,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oxmyran, Oxmyran, Mpd</t>
+          <t>Himmelsmyran, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597306</v>
+        <v>597356</v>
       </c>
       <c r="R23" t="n">
-        <v>6923901</v>
+        <v>6923925</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3048,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3058,7 +3022,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3073,15 +3042,1031 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124944576</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>597079</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6924029</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124426368</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tjäder, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>597061</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6924025</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124652643</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tjäder, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>597090</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6924039</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124653184</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tjäder, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>596989</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6924092</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Under tall.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124940732</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>597097</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6923890</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124941301</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>597175</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6923914</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124942316</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Oxmyran, Oxmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>597362</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6923870</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>124943230</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>597393</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6923922</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>124942395</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Himmelsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>597242</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6923954</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20024-2025 artfynd.xlsx
+++ b/artfynd/A 20024-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941910</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124943491</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941214</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941477</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941736</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941987</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124942320</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124943247</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124943420</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124943672</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124943798</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941680</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941845</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124942008</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124943160</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2379,6 +2459,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124653753</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2481,6 +2566,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124655249</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2593,6 +2683,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124943857</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124943977</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124944043</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,6 +3039,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941126</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3051,6 +3161,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124942488</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3168,6 +3283,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124944576</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3284,6 +3404,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124426368</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3389,6 +3514,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124652643</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3499,6 +3629,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124653184</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3611,6 +3746,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124940732</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3723,6 +3863,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124941301</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3844,6 +3989,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124942316</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3956,6 +4106,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124943230</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4067,8 +4222,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124942395</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>